--- a/4.3.4 фурье-оптика/измерения.xlsx
+++ b/4.3.4 фурье-оптика/измерения.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14750" windowHeight="7260" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14750" windowHeight="7260"/>
   </bookViews>
   <sheets>
     <sheet name="А1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>b1, cm</t>
   </si>
@@ -112,13 +112,16 @@
   <si>
     <t>сетка 3</t>
   </si>
+  <si>
+    <t>x, mkm*10</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -152,7 +155,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -249,10 +252,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>А1!$A$3:$A$16</c:f>
+              <c:f>А1!$A$3:$A$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -294,16 +297,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>А1!$B$3:$B$16</c:f>
+              <c:f>А1!$B$3:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.25</c:v>
                 </c:pt>
@@ -345,6 +351,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -359,11 +368,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="369283720"/>
-        <c:axId val="369282936"/>
+        <c:axId val="340867624"/>
+        <c:axId val="337987472"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="369283720"/>
+        <c:axId val="340867624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -420,12 +429,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="369282936"/>
+        <c:crossAx val="337987472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="369282936"/>
+        <c:axId val="337987472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -482,7 +491,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="369283720"/>
+        <c:crossAx val="340867624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -701,11 +710,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="349592536"/>
-        <c:axId val="349599200"/>
+        <c:axId val="339846024"/>
+        <c:axId val="341322648"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="349592536"/>
+        <c:axId val="339846024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -762,12 +771,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="349599200"/>
+        <c:crossAx val="341322648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="349599200"/>
+        <c:axId val="341322648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -824,7 +833,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="349592536"/>
+        <c:crossAx val="339846024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1989,16 +1998,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2340,7 +2349,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>

--- a/4.3.4 фурье-оптика/измерения.xlsx
+++ b/4.3.4 фурье-оптика/измерения.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14750" windowHeight="7260"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14750" windowHeight="7260" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="А1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>b1, cm</t>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t>D1, cm</t>
-  </si>
-  <si>
-    <t>x, mkm</t>
   </si>
   <si>
     <t>винт</t>
@@ -60,9 +57,6 @@
   </si>
   <si>
     <t>m</t>
-  </si>
-  <si>
-    <t>x0, mkm</t>
   </si>
   <si>
     <t>m (порядок максимума (придется думать головой))</t>
@@ -115,6 +109,15 @@
   <si>
     <t>x, mkm*10</t>
   </si>
+  <si>
+    <t>x, 10*mkm</t>
+  </si>
+  <si>
+    <t>x0, 10*mkm</t>
+  </si>
+  <si>
+    <t>F3, mm</t>
+  </si>
 </sst>
 </file>
 
@@ -153,10 +156,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -189,7 +195,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -368,11 +373,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="340867624"/>
-        <c:axId val="337987472"/>
+        <c:axId val="340423088"/>
+        <c:axId val="340422696"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="340867624"/>
+        <c:axId val="340423088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -429,12 +434,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="337987472"/>
+        <c:crossAx val="340422696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="337987472"/>
+        <c:axId val="340422696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -491,7 +496,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="340867624"/>
+        <c:crossAx val="340423088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -555,7 +560,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -665,37 +669,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0.32258064516129031</c:v>
+                  <c:v>0.70967741935483875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.625</c:v>
+                  <c:v>1.328125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>1.5833333333333333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.86956521739130432</c:v>
+                  <c:v>1.826086956521739</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.98039215686274517</c:v>
+                  <c:v>2.0588235294117649</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.1363636363636362</c:v>
+                  <c:v>2.3863636363636362</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.25</c:v>
+                  <c:v>2.625</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3513513513513513</c:v>
+                  <c:v>2.8378378378378377</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.639344262295082</c:v>
+                  <c:v>3.4426229508196724</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5</c:v>
+                  <c:v>1.0833333333333333</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.21739130434782611</c:v>
+                  <c:v>0.5434782608695653</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -710,11 +714,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="339846024"/>
-        <c:axId val="341322648"/>
+        <c:axId val="340421912"/>
+        <c:axId val="340422304"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="339846024"/>
+        <c:axId val="340421912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -771,12 +775,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="341322648"/>
+        <c:crossAx val="340422304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="341322648"/>
+        <c:axId val="340422304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -833,7 +837,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="339846024"/>
+        <c:crossAx val="340421912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2335,10 +2339,10 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -2349,13 +2353,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>131</v>
@@ -2498,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.90625" bestFit="1" customWidth="1"/>
@@ -2506,22 +2510,22 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -2529,7 +2533,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>14</v>
@@ -2552,8 +2556,8 @@
         <v>14</v>
       </c>
       <c r="D3">
-        <f>B3/A3</f>
-        <v>0.32258064516129031</v>
+        <f>(2*B3+1)/A3</f>
+        <v>0.70967741935483875</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -2567,8 +2571,8 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D13" si="0">B4/A4</f>
-        <v>0.625</v>
+        <f t="shared" ref="D4:D13" si="0">(2*B4+1)/A4</f>
+        <v>1.328125</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -2583,7 +2587,7 @@
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>1.5833333333333333</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
@@ -2598,7 +2602,7 @@
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
-        <v>0.86956521739130432</v>
+        <v>1.826086956521739</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
@@ -2613,7 +2617,7 @@
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.98039215686274517</v>
+        <v>2.0588235294117649</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
@@ -2628,7 +2632,7 @@
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>1.1363636363636362</v>
+        <v>2.3863636363636362</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
@@ -2643,7 +2647,7 @@
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>1.25</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
@@ -2658,7 +2662,7 @@
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>1.3513513513513513</v>
+        <v>2.8378378378378377</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -2673,7 +2677,7 @@
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>1.639344262295082</v>
+        <v>3.4426229508196724</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -2688,7 +2692,7 @@
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1.0833333333333333</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -2703,12 +2707,81 @@
       </c>
       <c r="D13">
         <f t="shared" si="0"/>
-        <v>0.21739130434782611</v>
-      </c>
+        <v>0.5434782608695653</v>
+      </c>
+    </row>
+    <row r="22" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="7:8" x14ac:dyDescent="0.35">
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2718,28 +2791,29 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>20</v>
-      </c>
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3"/>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -2763,6 +2837,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2774,33 +2851,33 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -2825,12 +2902,12 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>110</v>
@@ -2844,6 +2921,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2854,33 +2932,33 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -2905,10 +2983,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="G11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2921,6 +2999,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2931,7 +3010,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2946,7 +3025,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1">
         <v>110</v>
@@ -2954,7 +3033,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>38</v>
@@ -2962,7 +3041,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>25</v>
